--- a/dapan/cau 2.xlsx
+++ b/dapan/cau 2.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\New folder (7)\cb2505004\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\quiz-search\dapan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16940" windowHeight="11490"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16935" windowHeight="11490"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -147,24 +147,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -203,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -214,20 +202,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -235,11 +217,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -522,37 +507,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.7265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.26953125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.81640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="27" style="2" customWidth="1"/>
     <col min="8" max="9" width="9" style="2"/>
-    <col min="10" max="10" width="22.453125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="22.42578125" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -566,365 +551,365 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="12">
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7" t="str">
+      <c r="C4" s="5" t="str">
         <f>VLOOKUP(LEFT(B4,2),$I$4:$J$8,2,0)</f>
         <v>Petrolimex</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>1</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <f>IF(RIGHT(B4,1)="A",45000,62000)</f>
         <v>45000</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>90</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="11">
         <f>F4*E4</f>
         <v>4050000</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="4" t="s">
+      <c r="H4" s="4"/>
+      <c r="I4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="12">
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="5" t="str">
         <f t="shared" ref="C5:C13" si="0">VLOOKUP(LEFT(B5,2),$I$4:$J$8,2,0)</f>
         <v>VT Gas</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>2</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <f t="shared" ref="E5:E13" si="1">IF(RIGHT(B5,1)="A",45000,62000)</f>
         <v>62000</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>120</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="11">
         <f t="shared" ref="G5:G13" si="2">F5*E5</f>
         <v>7440000</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6" t="s">
+      <c r="H5" s="4"/>
+      <c r="I5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="12">
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="7" t="str">
+      <c r="C6" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Sài Gòn Petro</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>1</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>70</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="11">
         <f t="shared" si="2"/>
         <v>3150000</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6" t="s">
+      <c r="H6" s="4"/>
+      <c r="I6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="12">
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>4</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="5" t="str">
         <f t="shared" si="0"/>
         <v>VT Gas</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>1</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>160</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="11">
         <f t="shared" si="2"/>
         <v>7200000</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6" t="s">
+      <c r="H7" s="4"/>
+      <c r="I7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>18</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>5</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Elf Gas</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>2</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <f t="shared" si="1"/>
         <v>62000</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>60</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="11">
         <f t="shared" si="2"/>
         <v>3720000</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="6" t="s">
+      <c r="H8" s="4"/>
+      <c r="I8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="12">
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>6</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="7" t="str">
+      <c r="C9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Petrolimex</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>2</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <f t="shared" si="1"/>
         <v>62000</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>75</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="11">
         <f t="shared" si="2"/>
         <v>4650000</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="12">
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>7</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="7" t="str">
+      <c r="C10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Sài Gòn Petro</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>2</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>65</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="11">
         <f t="shared" si="2"/>
         <v>2925000</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="12">
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>8</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="7" t="str">
+      <c r="C11" s="5" t="str">
         <f t="shared" si="0"/>
         <v>VT Gas</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>1</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>98</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="11">
         <f t="shared" si="2"/>
         <v>4410000</v>
       </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="12">
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>9</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="7" t="str">
+      <c r="C12" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Elf Gas</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>1</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>130</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="11">
         <f t="shared" si="2"/>
         <v>5850000</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="12">
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="7" t="str">
+      <c r="C13" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Petrolimex</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>2</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <f t="shared" si="1"/>
         <v>62000</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>180</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="11">
         <f t="shared" si="2"/>
         <v>11160000</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -938,7 +923,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -952,7 +937,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -966,7 +951,7 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -980,7 +965,7 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>

--- a/dapan/cau 2.xlsx
+++ b/dapan/cau 2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\cb2508170\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\quiz-search\dapan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -136,8 +136,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="#,##0\ [$VNĐ]"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -228,13 +229,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -517,38 +518,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:G20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" style="12" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="12" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" style="12" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="1" width="5.7265625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="22.26953125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="24.1796875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="14.54296875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="24.7265625" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="9.1796875" style="10"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:7" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D3" s="13" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="1:7" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="D3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="12">
         <v>2340000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="3" customFormat="1" ht="35" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -571,7 +572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -592,12 +593,12 @@
         <f>IF(LEFT(B5,2)="HT",1000000,IF(LEFT(B5,2)="PH",800000,IF(LEFT(B5,2)="CN",500000,300000)))</f>
         <v>1000000</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="14">
         <f>$E$3*E5+F5</f>
         <v>19720000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -618,12 +619,12 @@
         <f t="shared" ref="F6:F12" si="1">IF(LEFT(B6,2)="HT",1000000,IF(LEFT(B6,2)="PH",800000,IF(LEFT(B6,2)="CN",500000,300000)))</f>
         <v>500000</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="14">
         <f t="shared" ref="G6:G12" si="2">$E$3*E6+F6</f>
         <v>15008000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -644,12 +645,12 @@
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="14">
         <f t="shared" si="2"/>
         <v>13872000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -670,12 +671,12 @@
         <f t="shared" si="1"/>
         <v>800000</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="14">
         <f t="shared" si="2"/>
         <v>18584000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -696,12 +697,12 @@
         <f t="shared" si="1"/>
         <v>500000</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="14">
         <f t="shared" si="2"/>
         <v>16880000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -722,12 +723,12 @@
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="14">
         <f t="shared" si="2"/>
         <v>14340000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -748,12 +749,12 @@
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="14">
         <f t="shared" si="2"/>
         <v>14340000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -774,19 +775,19 @@
         <f t="shared" si="1"/>
         <v>500000</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="14">
         <f t="shared" si="2"/>
         <v>15476000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+    <row r="15" spans="1:7" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-    </row>
-    <row r="16" spans="1:7" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+    </row>
+    <row r="16" spans="1:7" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A16" s="8"/>
       <c r="B16" s="9" t="s">
         <v>3</v>
@@ -795,7 +796,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A17" s="8"/>
       <c r="B17" s="5" t="s">
         <v>27</v>
@@ -804,7 +805,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A18" s="8"/>
       <c r="B18" s="5" t="s">
         <v>29</v>
@@ -813,7 +814,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A19" s="8"/>
       <c r="B19" s="5" t="s">
         <v>31</v>
@@ -822,7 +823,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="7" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A20" s="8"/>
       <c r="B20" s="5" t="s">
         <v>33</v>

--- a/dapan/cau 2.xlsx
+++ b/dapan/cau 2.xlsx
@@ -1,23 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\quiz-search\dapan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\quiz-search\dapan\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C66E393-A9BE-45A6-A9D2-C587CF0CEA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -135,7 +150,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0\ [$VNĐ]"/>
@@ -232,10 +247,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -516,32 +531,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:G20"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.7265625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="22.26953125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="24.1796875" style="10" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="16.453125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="24.7265625" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="9.1796875" style="10"/>
+    <col min="1" max="1" width="5.77734375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="26.77734375" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="9.21875" style="10"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-    </row>
-    <row r="3" spans="1:7" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="D3" s="11" t="s">
         <v>1</v>
       </c>
@@ -549,7 +564,7 @@
         <v>2340000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="3" customFormat="1" ht="35" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" s="3" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -572,7 +587,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -593,12 +608,12 @@
         <f>IF(LEFT(B5,2)="HT",1000000,IF(LEFT(B5,2)="PH",800000,IF(LEFT(B5,2)="CN",500000,300000)))</f>
         <v>1000000</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <f>$E$3*E5+F5</f>
         <v>19720000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -619,12 +634,12 @@
         <f t="shared" ref="F6:F12" si="1">IF(LEFT(B6,2)="HT",1000000,IF(LEFT(B6,2)="PH",800000,IF(LEFT(B6,2)="CN",500000,300000)))</f>
         <v>500000</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <f t="shared" ref="G6:G12" si="2">$E$3*E6+F6</f>
         <v>15008000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -645,12 +660,12 @@
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="13">
         <f t="shared" si="2"/>
         <v>13872000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -671,12 +686,12 @@
         <f t="shared" si="1"/>
         <v>800000</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <f t="shared" si="2"/>
         <v>18584000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -697,12 +712,12 @@
         <f t="shared" si="1"/>
         <v>500000</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="13">
         <f t="shared" si="2"/>
         <v>16880000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -723,12 +738,12 @@
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="13">
         <f t="shared" si="2"/>
         <v>14340000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -749,12 +764,12 @@
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <f t="shared" si="2"/>
         <v>14340000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -775,19 +790,19 @@
         <f t="shared" si="1"/>
         <v>500000</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="13">
         <f t="shared" si="2"/>
         <v>15476000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="13" t="s">
+    <row r="15" spans="1:7" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-    </row>
-    <row r="16" spans="1:7" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+    </row>
+    <row r="16" spans="1:7" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
       <c r="B16" s="9" t="s">
         <v>3</v>
@@ -796,7 +811,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" s="8"/>
       <c r="B17" s="5" t="s">
         <v>27</v>
@@ -805,7 +820,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="5" t="s">
         <v>29</v>
@@ -814,7 +829,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="5" t="s">
         <v>31</v>
@@ -823,7 +838,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="7" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A20" s="8"/>
       <c r="B20" s="5" t="s">
         <v>33</v>

--- a/dapan/cau 2.xlsx
+++ b/dapan/cau 2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\New folder\quiz-search\dapan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\New folder\quiz-search\dapan\cb2602062\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317001E6-6D39-4DBE-914E-F3EA65C212E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F4DABE-3814-46D0-AB67-341EE8B59121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,9 +299,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -332,10 +329,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -628,256 +628,256 @@
     <col min="4" max="4" width="24.21875" style="5" customWidth="1"/>
     <col min="5" max="5" width="14.5546875" style="5" customWidth="1"/>
     <col min="6" max="6" width="16.44140625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="26.77734375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" style="5" customWidth="1"/>
     <col min="8" max="16384" width="9.21875" style="5"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>2340000</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="1" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="11">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="12" t="str">
+      <c r="D5" s="11" t="str">
         <f>VLOOKUP(LEFT(B5,2),$B$16:$C$20,2,0)</f>
         <v xml:space="preserve">Hiệu trưởng </v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <v>8</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <f>IF(LEFT(B5,2)="HT",1000000,IF(LEFT(B5,2)="PH",800000,IF(LEFT(B5,2)="CN",500000,300000)))</f>
         <v>1000000</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <f>$E$3*E5+F5</f>
         <v>19720000</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="16" t="str">
+      <c r="D6" s="15" t="str">
         <f t="shared" ref="D6:D12" si="0">VLOOKUP(LEFT(B6,2),$B$16:$C$20,2,0)</f>
         <v>Chủ nhiệm bộ môn</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="15">
         <v>6.2</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="16">
         <f t="shared" ref="F6:F12" si="1">IF(LEFT(B6,2)="HT",1000000,IF(LEFT(B6,2)="PH",800000,IF(LEFT(B6,2)="CN",500000,300000)))</f>
         <v>500000</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="17">
         <f t="shared" ref="G6:G12" si="2">$E$3*E6+F6</f>
         <v>15008000</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="16" t="str">
+      <c r="D7" s="15" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Giáo viên </v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="15">
         <v>5.8</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="16">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <f t="shared" si="2"/>
         <v>13872000</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="16" t="str">
+      <c r="D8" s="15" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Phó hiêu trưởng </v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <v>7.6</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="16">
         <f t="shared" si="1"/>
         <v>800000</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="17">
         <f t="shared" si="2"/>
         <v>18584000</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="16" t="str">
+      <c r="D9" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Chủ nhiệm bộ môn</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <v>7</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="16">
         <f t="shared" si="1"/>
         <v>500000</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="17">
         <f t="shared" si="2"/>
         <v>16880000</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="16" t="str">
+      <c r="D10" s="15" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Giáo viên </v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="15">
         <v>6</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="16">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="17">
         <f t="shared" si="2"/>
         <v>14340000</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="16" t="str">
+      <c r="D11" s="15" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Giáo viên </v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>6</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="16">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <f t="shared" si="2"/>
         <v>14340000</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="19">
+      <c r="A12" s="18">
         <v>8</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="20" t="str">
+      <c r="D12" s="19" t="str">
         <f t="shared" si="0"/>
         <v>Chủ nhiệm bộ môn</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="19">
         <v>6.4</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="20">
         <f t="shared" si="1"/>
         <v>500000</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="21">
         <f t="shared" si="2"/>
         <v>15476000</v>
       </c>
@@ -891,10 +891,10 @@
     </row>
     <row r="16" spans="1:7" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="22" t="s">
         <v>26</v>
       </c>
     </row>
